--- a/gst_recon/sample_data/gstr2b_2025-04.xlsx
+++ b/gst_recon/sample_data/gstr2b_2025-04.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U29"/>
+  <dimension ref="A1:U31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2359,17 +2359,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07AAGFD1357Q1Z2</t>
+          <t>27AAJFA2468S1ZQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Delhi Office Supplies</t>
+          <t>Annapurna Caterers</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DOS-1001</t>
+          <t>ANC/77</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2379,11 +2379,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>28-03-2025</t>
+          <t>18-04-2025</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>11210</v>
+        <v>9440</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2396,23 +2396,23 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>9500</v>
+        <v>8000</v>
       </c>
       <c r="J29" t="n">
-        <v>1710</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Mar'25</t>
+          <t>Apr'25</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2433,6 +2433,162 @@
       </c>
       <c r="T29" t="inlineStr"/>
       <c r="U29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>27ABKPS1357T1ZO</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Shree Roadways (GTA)</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>SRW-310</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>08-04-2025</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>21000</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>27-Maharashtra</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>20000</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" t="n">
+        <v>500</v>
+      </c>
+      <c r="L30" t="n">
+        <v>500</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Apr'25</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>11-05-2025</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>e-Invoice</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>07AAGFD1357Q1Z2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Delhi Office Supplies</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DOS-1001</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>28-03-2025</t>
+        </is>
+      </c>
+      <c r="F31" t="n">
+        <v>11210</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>27-Maharashtra</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>9500</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1710</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Mar'25</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>11-05-2025</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>e-Invoice</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
